--- a/data/evaluation_results_2.xlsx
+++ b/data/evaluation_results_2.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -522,27 +516,24 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student who is caught wearing a non-uniform is detention or a warning, followed by a parent contact or meeting.</t>
+          <t>The most likely consequence for the student who is caught wearing a non-uniform is detention or a warning, followed by a possible meeting with the teacher or school administrator to discuss the infraction and the importance of adhering to the uniform policy.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:03:52.344124+00:00</t>
+          <t>2026-10-22T04:31:01.576954+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.4104014239999287</v>
+        <v>0.564168267000241</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.4276163539999516</v>
+        <v>80</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -568,22 +559,19 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:03:52.772032+00:00</t>
+          <t>2026-10-22T04:31:02.141422+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.3667489979999345</v>
+        <v>0.4000182199997653</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.3832810220000056</v>
+        <v>80</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J3" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -604,27 +592,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student who is caught wearing a non-uniform would be a verbal warning or a detention, as a first-time offense. However, if the student is caught wearing a non-uniform for the second time, the consequence may escalate to a parent-teacher conference or a more severe disciplinary action, such as a suspension or a loss of privileges.</t>
+          <t>The most likely consequence for the student who is caught wearing a non-uniform would be a verbal warning or a detention, as a first-time offense. However, if the student has a history of violating the uniform policy or if the infraction is severe, the consequence could be more severe, such as a parent-teacher conference, a written warning, or even a suspension or detention for a longer period.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:03:53.155528+00:00</t>
+          <t>2026-10-22T04:31:02.541641+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7930914229999644</v>
+        <v>0.7919799760002206</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8093196249999437</v>
+        <v>80</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -644,6 +629,54 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>To find the cost of the ball, we can set up an equation. Let's say the cost of the ball is x.
+Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
+The total cost of the bat and the ball together is $1.10, so we can set up the equation:
+x + (x + $1.00) = $1.10
+Combine like terms:
+2x + $1.00 = $1.10
+Subtract $1.00 from both sides:
+2x = $0.10
+Divide both sides by 2:
+x = $0.05
+So, the ball costs $0.05.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:03.333841+00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1.368997068999761</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>To find the cost of the ball, we need to set up an equation. Let's say the cost of the ball is x.
 Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
@@ -658,45 +691,42 @@
 So, the ball costs $0.05.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:03:53.965093+00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1.399280021999971</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>1.415868049999972</v>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:04.703114+00:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1.432226222999816</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>To find the cost of the ball, we need to set up an equation. Let's say the cost of the ball is x.
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>To find the cost of the ball, we can set up an equation. Let's say the cost of the ball is x.
 Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
 The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
@@ -709,75 +739,21 @@
 So, the ball costs $0.05.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:03:55.381206+00:00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1.424338100999989</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1.442743381000014</v>
-      </c>
-      <c r="I6" s="2" t="n">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:06.135580+00:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1.425377709999793</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>To find the cost of the ball, we need to set up an equation. Let's say the cost of the ball is x.
-Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
-The total cost of the bat and the ball together is $1.10, so we can set up the equation:
-x + (x + $1.00) = $1.10
-Combine like terms:
-2x + $1.00 = $1.10
-Subtract $1.00 from both sides:
-2x = $0.10
-Divide both sides by 2:
-x = $0.05
-So, the ball costs $0.05.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:03:56.824186+00:00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1.368964406000032</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1.386680781999985</v>
-      </c>
       <c r="I7" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -800,31 +776,27 @@
         <is>
           <t>To solve this problem, we need to calculate the net progress of the snail each day.
 The snail climbs 3 feet up during the day, but slips back 2 feet at night, resulting in a net progress of 3 - 2 = 1 foot per day.
-Since the well is 20 feet deep, we need to find out how many days it will take for the snail to cover this distance.
-To do this, we can divide the total depth of the well (20 feet) by the net progress of the snail per day (1 foot).
+Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
+To find the number of days it will take for the snail to reach the top, we can divide the total depth of the well (20 feet) by the net progress of the snail per day (1 foot):
 20 feet / 1 foot per day = 20 days
-However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back because it has already reached the top. Therefore, we don't need to count the 20th day as a full day of progress.
-So, the snail will reach the top of the well on the 20th day, but it will actually take 19 days of net progress (18 days of climbing and 1 day of slipping back) to reach the top.</t>
+Therefore, it will take the snail 20 days to reach the top of the well.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:03:58.211093+00:00</t>
+          <t>2026-10-22T04:31:07.561168+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2.221693109999933</v>
+        <v>1.619266651000089</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.247798450000005</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>239</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>163</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -847,30 +819,27 @@
         <is>
           <t>To solve this problem, we need to calculate the net progress of the snail each day.
 The snail climbs 3 feet up during the day, but slips back 2 feet at night, resulting in a net progress of 3 - 2 = 1 foot per day.
-Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
-To find the number of days required, we can divide the total depth of the well by the net progress of the snail per day:
-20 feet (total depth) / 1 foot (net progress per day) = 20 days
+Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top. 
+To find the number of days it will take for the snail to reach the top, we can divide the total depth of the well (20 feet) by the net progress of the snail per day (1 foot).
+20 feet / 1 foot per day = 20 days
 Therefore, it will take the snail 20 days to reach the top of the well.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:04:00.459318+00:00</t>
+          <t>2026-10-22T04:31:09.180817+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.487053489000004</v>
+        <v>1.485420283999701</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.519232342000009</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -891,35 +860,32 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>To solve this problem, we need to calculate the net progress of the snail each day.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night, resulting in a net progress of 1 foot per day.
-Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
-To find the number of days required, we can divide the total depth of the well (20 feet) by the net progress of the snail (1 foot) per day.
+          <t>To solve this problem, let's break it down step by step.
+The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up the well each day.
+Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top.
+To find the number of days it will take for the snail to reach the top, we can divide the total depth of the well (20 feet) by the effective daily progress (1 foot):
 20 feet / 1 foot per day = 20 days
-Therefore, it will take the snail 20 days to reach the top of the well.</t>
+However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back at night because it has already reached the top. Therefore, the correct answer is 20 days.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:04:01.978886+00:00</t>
+          <t>2026-10-22T04:31:10.666506+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.312012772000003</v>
+        <v>1.601675199000056</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.338763484000083</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>175</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -991,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1019,10 +985,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 0.413,
-  "median_latency": 0.421,
+  "median_input": 81,
+  "median_output": 151,
+  "median_latency": 1.494,
   "correct_frequency": 0.8333333333333334,
-  "misinformation_frequency": 0
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1030,45 +998,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.413</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.421</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1106,7 +1094,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:04:04.659589+00:00</t>
+          <t>2026-10-22T04:31:13.576217+00:00</t>
         </is>
       </c>
     </row>
